--- a/output/pdf_financials_xlsx/XRI.xlsx
+++ b/output/pdf_financials_xlsx/XRI.xlsx
@@ -2197,16 +2197,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.014875</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.07729</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.23348</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.431135</v>
       </c>
     </row>
     <row r="93">
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>-0.045477</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>0.055977</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>0</v>
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.029534</v>
+        <v>-0.015943</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.08891</v>
+        <v>0.144887</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>0.105013</v>
@@ -3604,7 +3604,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -3826,7 +3830,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -3968,7 +3976,11 @@
           <t>Prepaid and deposits (Note 4)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
         <v>0.055977</v>
       </c>
@@ -4156,7 +4168,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" s="5" t="n">
         <v>0.014875</v>
       </c>
@@ -5340,7 +5356,11 @@
           <t>Prepaid and deposits</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E64" s="5" t="n">
         <v>-0.045477</v>
       </c>

--- a/output/pdf_financials_xlsx/XRI.xlsx
+++ b/output/pdf_financials_xlsx/XRI.xlsx
@@ -645,7 +645,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000319</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -948,7 +948,7 @@
         <v>-0.35528</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.581275</v>
+        <v>-0.5815940000000001</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-1.207951</v>
@@ -986,7 +986,7 @@
         <v>-0.35528</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.581275</v>
+        <v>-0.5815940000000001</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.207951</v>
@@ -1079,16 +1079,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.006153</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.106992</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.004807</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>5.484756</v>
       </c>
     </row>
     <row r="35">
@@ -1117,16 +1117,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.006153</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.106992</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.004807</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>5.484756</v>
       </c>
     </row>
     <row r="37">
@@ -1345,16 +1345,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.070428</v>
+        <v>0.064275</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.128114</v>
+        <v>0.021122</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.034782</v>
+        <v>0.029975</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>5.690255</v>
+        <v>0.205499</v>
       </c>
     </row>
     <row r="49">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">

--- a/output/pdf_financials_xlsx/XRI.xlsx
+++ b/output/pdf_financials_xlsx/XRI.xlsx
@@ -1714,16 +1714,16 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.046</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.108545</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.0177</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.036856</v>
       </c>
     </row>
     <row r="68">
@@ -5694,7 +5694,11 @@
           <t>Value of options issued on private placement $</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
